--- a/output/tempo_work_block_summary.xlsx
+++ b/output/tempo_work_block_summary.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2921,6 +2921,246 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>tempo_run</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>00:03:46</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>03:46</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>166</v>
+      </c>
+      <c r="I63" t="n">
+        <v>174</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>tempo_run</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>00:02:13</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>168</v>
+      </c>
+      <c r="I64" t="n">
+        <v>174</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>tempo_run</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>00:03:43</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>166</v>
+      </c>
+      <c r="I65" t="n">
+        <v>173</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>tempo_run</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>7</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>00:02:16</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>171</v>
+      </c>
+      <c r="I66" t="n">
+        <v>173</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>tempo_run</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="n">
+        <v>9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>00:03:44</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>168</v>
+      </c>
+      <c r="I67" t="n">
+        <v>175</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>tempo_run</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>00:02:15</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>03:41</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>173</v>
+      </c>
+      <c r="I68" t="n">
+        <v>176</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2932,7 +3172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3306,6 +3546,49 @@
         <v>24.02</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tempo_run</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>00:17:57</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>176</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
